--- a/reports/TDM_Steel_Bins_Details_2026.xlsx
+++ b/reports/TDM_Steel_Bins_Details_2026.xlsx
@@ -9,7 +9,10 @@
   <sheets>
     <sheet name="Steel Bins Details 2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Steel Bins Details 2025'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Steel Bins Details 2025'!$A$1:$M$33</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -145,7 +148,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -195,8 +198,12 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -564,7 +571,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1370,13 +1377,16 @@
       </c>
       <c r="M27" s="16" t="n"/>
     </row>
+    <row r="28"/>
     <row r="29" ht="25" customHeight="1">
       <c r="A29" s="17" t="inlineStr">
         <is>
           <t>Total no of steel Bin on the floor</t>
         </is>
       </c>
-      <c r="D29" s="18" t="n">
+      <c r="B29" s="18" t="n"/>
+      <c r="C29" s="18" t="n"/>
+      <c r="D29" s="19" t="n">
         <v>178</v>
       </c>
     </row>
@@ -1386,7 +1396,9 @@
           <t>Spare steel bin Available</t>
         </is>
       </c>
-      <c r="D30" s="18" t="n">
+      <c r="B30" s="18" t="n"/>
+      <c r="C30" s="18" t="n"/>
+      <c r="D30" s="19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1396,7 +1408,9 @@
           <t xml:space="preserve">Used &amp; damaged stock for Disposed </t>
         </is>
       </c>
-      <c r="D31" s="18" t="n">
+      <c r="B31" s="18" t="n"/>
+      <c r="C31" s="18" t="n"/>
+      <c r="D31" s="19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1406,7 +1420,9 @@
           <t xml:space="preserve">Bin Transfer </t>
         </is>
       </c>
-      <c r="D32" s="18" t="n"/>
+      <c r="B32" s="18" t="n"/>
+      <c r="C32" s="18" t="n"/>
+      <c r="D32" s="20" t="n"/>
     </row>
     <row r="33" ht="25" customHeight="1">
       <c r="A33" s="17" t="inlineStr">
@@ -1414,7 +1430,9 @@
           <t>Total  Steel bins</t>
         </is>
       </c>
-      <c r="D33" s="18">
+      <c r="B33" s="18" t="n"/>
+      <c r="C33" s="18" t="n"/>
+      <c r="D33" s="19">
         <f>SUM(D29+D30+D31)</f>
         <v/>
       </c>
@@ -1432,5 +1450,6 @@
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>